--- a/data/table_2025-11-25_13-54-25.xlsx
+++ b/data/table_2025-11-25_13-54-25.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma0026.NB-MA0026\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schneids\code\building-archetype-inference\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B8684-027A-4D1E-AC40-E8E27E82BDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66B5BA7-8078-481B-A6A0-5BC4A118EB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18744" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30816" yWindow="-2784" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenblatt 0" sheetId="3" r:id="rId1"/>
-    <sheet name="template_rse" sheetId="6" state="hidden" r:id="rId2"/>
-    <sheet name="format" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="clean" sheetId="7" r:id="rId2"/>
+    <sheet name="template_rse" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="format" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="72">
   <si>
     <t>heading</t>
   </si>
@@ -206,6 +207,51 @@
   </si>
   <si>
     <t>Zeitraum, in dem das Errichtungsdatum des Gebäudes liegt.</t>
+  </si>
+  <si>
+    <t>Nutzung</t>
+  </si>
+  <si>
+    <t>Bauperiode</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>NGF</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>res_single_u</t>
+  </si>
+  <si>
+    <t>res_double_u</t>
+  </si>
+  <si>
+    <t>res_multi_u</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>communication</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>leasure</t>
+  </si>
+  <si>
+    <t>hotel</t>
+  </si>
+  <si>
+    <t>hostel</t>
   </si>
 </sst>
 </file>
@@ -930,28 +976,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:E135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15.6640625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>15</v>
       </c>
@@ -964,7 +1010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>18</v>
       </c>
@@ -977,7 +1023,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -985,7 +1031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
@@ -999,7 +1045,7 @@
         <v>23473512</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="16"/>
       <c r="C11" s="8" t="s">
         <v>24</v>
@@ -1011,7 +1057,7 @@
         <v>11723038</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="16"/>
       <c r="C12" s="8" t="s">
         <v>25</v>
@@ -1023,7 +1069,7 @@
         <v>18161803</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="16"/>
       <c r="C13" s="8" t="s">
         <v>26</v>
@@ -1035,7 +1081,7 @@
         <v>21762413</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="16"/>
       <c r="C14" s="8" t="s">
         <v>27</v>
@@ -1047,7 +1093,7 @@
         <v>28584060</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="16"/>
       <c r="C15" s="8" t="s">
         <v>28</v>
@@ -1059,7 +1105,7 @@
         <v>30472547</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="16"/>
       <c r="C16" s="8" t="s">
         <v>29</v>
@@ -1071,7 +1117,7 @@
         <v>29020507</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="16"/>
       <c r="C17" s="8" t="s">
         <v>30</v>
@@ -1083,7 +1129,7 @@
         <v>17678057</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="16"/>
       <c r="C18" s="8" t="s">
         <v>31</v>
@@ -1095,7 +1141,7 @@
         <v>18753671</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="16"/>
       <c r="C19" s="8" t="s">
         <v>32</v>
@@ -1107,7 +1153,7 @@
         <v>16439405</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="16"/>
       <c r="C20" s="8" t="s">
         <v>33</v>
@@ -1119,7 +1165,7 @@
         <v>22950883</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="15" t="s">
         <v>34</v>
       </c>
@@ -1133,7 +1179,7 @@
         <v>10767691</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="16"/>
       <c r="C22" s="8" t="s">
         <v>24</v>
@@ -1145,7 +1191,7 @@
         <v>3849703</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="16"/>
       <c r="C23" s="8" t="s">
         <v>25</v>
@@ -1157,7 +1203,7 @@
         <v>7736326</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="16"/>
       <c r="C24" s="8" t="s">
         <v>26</v>
@@ -1169,7 +1215,7 @@
         <v>11347135</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="16"/>
       <c r="C25" s="8" t="s">
         <v>27</v>
@@ -1181,7 +1227,7 @@
         <v>14142151</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="16"/>
       <c r="C26" s="8" t="s">
         <v>28</v>
@@ -1193,7 +1239,7 @@
         <v>11442878</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="16"/>
       <c r="C27" s="8" t="s">
         <v>29</v>
@@ -1205,7 +1251,7 @@
         <v>5445645</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="16"/>
       <c r="C28" s="8" t="s">
         <v>30</v>
@@ -1217,7 +1263,7 @@
         <v>2588319</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="16"/>
       <c r="C29" s="8" t="s">
         <v>31</v>
@@ -1229,7 +1275,7 @@
         <v>2743955</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="16"/>
       <c r="C30" s="8" t="s">
         <v>32</v>
@@ -1241,7 +1287,7 @@
         <v>1333113</v>
       </c>
     </row>
-    <row r="31" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="16"/>
       <c r="C31" s="8" t="s">
         <v>33</v>
@@ -1253,7 +1299,7 @@
         <v>2038252</v>
       </c>
     </row>
-    <row r="32" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="15" t="s">
         <v>35</v>
       </c>
@@ -1267,7 +1313,7 @@
         <v>39061683</v>
       </c>
     </row>
-    <row r="33" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="16"/>
       <c r="C33" s="8" t="s">
         <v>24</v>
@@ -1279,7 +1325,7 @@
         <v>12527868</v>
       </c>
     </row>
-    <row r="34" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="16"/>
       <c r="C34" s="8" t="s">
         <v>25</v>
@@ -1291,7 +1337,7 @@
         <v>17158733</v>
       </c>
     </row>
-    <row r="35" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="16"/>
       <c r="C35" s="8" t="s">
         <v>26</v>
@@ -1303,7 +1349,7 @@
         <v>24662498</v>
       </c>
     </row>
-    <row r="36" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="16"/>
       <c r="C36" s="8" t="s">
         <v>27</v>
@@ -1315,7 +1361,7 @@
         <v>26287600</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="16"/>
       <c r="C37" s="8" t="s">
         <v>28</v>
@@ -1327,7 +1373,7 @@
         <v>19572979</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="16"/>
       <c r="C38" s="8" t="s">
         <v>29</v>
@@ -1339,7 +1385,7 @@
         <v>19795355</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="16"/>
       <c r="C39" s="8" t="s">
         <v>30</v>
@@ -1351,7 +1397,7 @@
         <v>10075909</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B40" s="16"/>
       <c r="C40" s="8" t="s">
         <v>31</v>
@@ -1363,7 +1409,7 @@
         <v>13405270</v>
       </c>
     </row>
-    <row r="41" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="16"/>
       <c r="C41" s="8" t="s">
         <v>32</v>
@@ -1375,7 +1421,7 @@
         <v>15425698</v>
       </c>
     </row>
-    <row r="42" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="16"/>
       <c r="C42" s="8" t="s">
         <v>33</v>
@@ -1387,7 +1433,7 @@
         <v>30950654</v>
       </c>
     </row>
-    <row r="43" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="s">
         <v>36</v>
       </c>
@@ -1401,7 +1447,7 @@
         <v>2607298</v>
       </c>
     </row>
-    <row r="44" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="16"/>
       <c r="C44" s="8" t="s">
         <v>24</v>
@@ -1413,7 +1459,7 @@
         <v>398091</v>
       </c>
     </row>
-    <row r="45" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B45" s="16"/>
       <c r="C45" s="8" t="s">
         <v>25</v>
@@ -1425,7 +1471,7 @@
         <v>690729</v>
       </c>
     </row>
-    <row r="46" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="16"/>
       <c r="C46" s="8" t="s">
         <v>26</v>
@@ -1437,7 +1483,7 @@
         <v>1321961</v>
       </c>
     </row>
-    <row r="47" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="16"/>
       <c r="C47" s="8" t="s">
         <v>27</v>
@@ -1449,7 +1495,7 @@
         <v>2126974</v>
       </c>
     </row>
-    <row r="48" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="16"/>
       <c r="C48" s="8" t="s">
         <v>28</v>
@@ -1461,7 +1507,7 @@
         <v>1707731</v>
       </c>
     </row>
-    <row r="49" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="16"/>
       <c r="C49" s="8" t="s">
         <v>29</v>
@@ -1473,7 +1519,7 @@
         <v>1267725</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="16"/>
       <c r="C50" s="8" t="s">
         <v>30</v>
@@ -1485,7 +1531,7 @@
         <v>860823</v>
       </c>
     </row>
-    <row r="51" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B51" s="16"/>
       <c r="C51" s="8" t="s">
         <v>31</v>
@@ -1497,7 +1543,7 @@
         <v>1308710</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" s="16"/>
       <c r="C52" s="8" t="s">
         <v>32</v>
@@ -1509,7 +1555,7 @@
         <v>1117495</v>
       </c>
     </row>
-    <row r="53" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B53" s="16"/>
       <c r="C53" s="8" t="s">
         <v>33</v>
@@ -1521,7 +1567,7 @@
         <v>1045035</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B54" s="15" t="s">
         <v>37</v>
       </c>
@@ -1535,7 +1581,7 @@
         <v>8930436</v>
       </c>
     </row>
-    <row r="55" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B55" s="16"/>
       <c r="C55" s="8" t="s">
         <v>24</v>
@@ -1547,7 +1593,7 @@
         <v>1909084</v>
       </c>
     </row>
-    <row r="56" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B56" s="16"/>
       <c r="C56" s="8" t="s">
         <v>25</v>
@@ -1559,7 +1605,7 @@
         <v>2977270</v>
       </c>
     </row>
-    <row r="57" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B57" s="16"/>
       <c r="C57" s="8" t="s">
         <v>26</v>
@@ -1571,7 +1617,7 @@
         <v>4736247</v>
       </c>
     </row>
-    <row r="58" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B58" s="16"/>
       <c r="C58" s="8" t="s">
         <v>27</v>
@@ -1583,7 +1629,7 @@
         <v>7340020</v>
       </c>
     </row>
-    <row r="59" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B59" s="16"/>
       <c r="C59" s="8" t="s">
         <v>28</v>
@@ -1595,7 +1641,7 @@
         <v>5895871</v>
       </c>
     </row>
-    <row r="60" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B60" s="16"/>
       <c r="C60" s="8" t="s">
         <v>29</v>
@@ -1607,7 +1653,7 @@
         <v>2213135</v>
       </c>
     </row>
-    <row r="61" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B61" s="16"/>
       <c r="C61" s="8" t="s">
         <v>30</v>
@@ -1619,7 +1665,7 @@
         <v>1562845</v>
       </c>
     </row>
-    <row r="62" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B62" s="16"/>
       <c r="C62" s="8" t="s">
         <v>31</v>
@@ -1631,7 +1677,7 @@
         <v>2472381</v>
       </c>
     </row>
-    <row r="63" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B63" s="16"/>
       <c r="C63" s="8" t="s">
         <v>32</v>
@@ -1643,7 +1689,7 @@
         <v>1324973</v>
       </c>
     </row>
-    <row r="64" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B64" s="16"/>
       <c r="C64" s="8" t="s">
         <v>33</v>
@@ -1655,7 +1701,7 @@
         <v>2111180</v>
       </c>
     </row>
-    <row r="65" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" s="15" t="s">
         <v>38</v>
       </c>
@@ -1669,7 +1715,7 @@
         <v>12265087</v>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="16"/>
       <c r="C66" s="8" t="s">
         <v>24</v>
@@ -1681,7 +1727,7 @@
         <v>2759625</v>
       </c>
     </row>
-    <row r="67" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67" s="16"/>
       <c r="C67" s="8" t="s">
         <v>25</v>
@@ -1693,7 +1739,7 @@
         <v>4531756</v>
       </c>
     </row>
-    <row r="68" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68" s="16"/>
       <c r="C68" s="8" t="s">
         <v>26</v>
@@ -1705,7 +1751,7 @@
         <v>5438261</v>
       </c>
     </row>
-    <row r="69" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69" s="16"/>
       <c r="C69" s="8" t="s">
         <v>27</v>
@@ -1717,7 +1763,7 @@
         <v>7922004</v>
       </c>
     </row>
-    <row r="70" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70" s="16"/>
       <c r="C70" s="8" t="s">
         <v>28</v>
@@ -1729,7 +1775,7 @@
         <v>8059904</v>
       </c>
     </row>
-    <row r="71" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71" s="16"/>
       <c r="C71" s="8" t="s">
         <v>29</v>
@@ -1741,7 +1787,7 @@
         <v>5092184</v>
       </c>
     </row>
-    <row r="72" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72" s="16"/>
       <c r="C72" s="8" t="s">
         <v>30</v>
@@ -1753,7 +1799,7 @@
         <v>3369820</v>
       </c>
     </row>
-    <row r="73" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73" s="16"/>
       <c r="C73" s="8" t="s">
         <v>31</v>
@@ -1765,7 +1811,7 @@
         <v>4224545</v>
       </c>
     </row>
-    <row r="74" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" s="16"/>
       <c r="C74" s="8" t="s">
         <v>32</v>
@@ -1777,7 +1823,7 @@
         <v>2730904</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75" s="16"/>
       <c r="C75" s="8" t="s">
         <v>33</v>
@@ -1789,7 +1835,7 @@
         <v>4442414</v>
       </c>
     </row>
-    <row r="76" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76" s="15" t="s">
         <v>39</v>
       </c>
@@ -1803,7 +1849,7 @@
         <v>6081724</v>
       </c>
     </row>
-    <row r="77" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B77" s="16"/>
       <c r="C77" s="8" t="s">
         <v>24</v>
@@ -1815,7 +1861,7 @@
         <v>1537935</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78" s="16"/>
       <c r="C78" s="8" t="s">
         <v>25</v>
@@ -1827,7 +1873,7 @@
         <v>2556072</v>
       </c>
     </row>
-    <row r="79" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79" s="16"/>
       <c r="C79" s="8" t="s">
         <v>26</v>
@@ -1839,7 +1885,7 @@
         <v>4864556</v>
       </c>
     </row>
-    <row r="80" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80" s="16"/>
       <c r="C80" s="8" t="s">
         <v>27</v>
@@ -1851,7 +1897,7 @@
         <v>7261274</v>
       </c>
     </row>
-    <row r="81" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81" s="16"/>
       <c r="C81" s="8" t="s">
         <v>28</v>
@@ -1863,7 +1909,7 @@
         <v>8486286</v>
       </c>
     </row>
-    <row r="82" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82" s="16"/>
       <c r="C82" s="8" t="s">
         <v>29</v>
@@ -1875,7 +1921,7 @@
         <v>6385102</v>
       </c>
     </row>
-    <row r="83" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B83" s="16"/>
       <c r="C83" s="8" t="s">
         <v>30</v>
@@ -1887,7 +1933,7 @@
         <v>3463391</v>
       </c>
     </row>
-    <row r="84" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B84" s="16"/>
       <c r="C84" s="8" t="s">
         <v>31</v>
@@ -1899,7 +1945,7 @@
         <v>4560708</v>
       </c>
     </row>
-    <row r="85" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B85" s="16"/>
       <c r="C85" s="8" t="s">
         <v>32</v>
@@ -1911,7 +1957,7 @@
         <v>2815379</v>
       </c>
     </row>
-    <row r="86" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B86" s="16"/>
       <c r="C86" s="8" t="s">
         <v>33</v>
@@ -1923,7 +1969,7 @@
         <v>3465770</v>
       </c>
     </row>
-    <row r="87" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B87" s="15" t="s">
         <v>40</v>
       </c>
@@ -1937,7 +1983,7 @@
         <v>1135984</v>
       </c>
     </row>
-    <row r="88" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B88" s="16"/>
       <c r="C88" s="8" t="s">
         <v>24</v>
@@ -1949,7 +1995,7 @@
         <v>443471</v>
       </c>
     </row>
-    <row r="89" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B89" s="16"/>
       <c r="C89" s="8" t="s">
         <v>25</v>
@@ -1961,7 +2007,7 @@
         <v>854886</v>
       </c>
     </row>
-    <row r="90" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B90" s="16"/>
       <c r="C90" s="8" t="s">
         <v>26</v>
@@ -1973,7 +2019,7 @@
         <v>964407</v>
       </c>
     </row>
-    <row r="91" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B91" s="16"/>
       <c r="C91" s="8" t="s">
         <v>27</v>
@@ -1985,7 +2031,7 @@
         <v>1414485</v>
       </c>
     </row>
-    <row r="92" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92" s="16"/>
       <c r="C92" s="8" t="s">
         <v>28</v>
@@ -1997,7 +2043,7 @@
         <v>1529938</v>
       </c>
     </row>
-    <row r="93" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93" s="16"/>
       <c r="C93" s="8" t="s">
         <v>29</v>
@@ -2009,7 +2055,7 @@
         <v>1256145</v>
       </c>
     </row>
-    <row r="94" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94" s="16"/>
       <c r="C94" s="8" t="s">
         <v>30</v>
@@ -2021,7 +2067,7 @@
         <v>647747</v>
       </c>
     </row>
-    <row r="95" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95" s="16"/>
       <c r="C95" s="8" t="s">
         <v>31</v>
@@ -2033,7 +2079,7 @@
         <v>922340</v>
       </c>
     </row>
-    <row r="96" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B96" s="16"/>
       <c r="C96" s="8" t="s">
         <v>32</v>
@@ -2045,7 +2091,7 @@
         <v>731982</v>
       </c>
     </row>
-    <row r="97" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B97" s="16"/>
       <c r="C97" s="8" t="s">
         <v>33</v>
@@ -2057,7 +2103,7 @@
         <v>888281</v>
       </c>
     </row>
-    <row r="98" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B98" s="15" t="s">
         <v>41</v>
       </c>
@@ -2071,7 +2117,7 @@
         <v>9987208</v>
       </c>
     </row>
-    <row r="99" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="16"/>
       <c r="C99" s="8" t="s">
         <v>24</v>
@@ -2083,7 +2129,7 @@
         <v>5410888</v>
       </c>
     </row>
-    <row r="100" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="16"/>
       <c r="C100" s="8" t="s">
         <v>25</v>
@@ -2095,7 +2141,7 @@
         <v>8242364</v>
       </c>
     </row>
-    <row r="101" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B101" s="16"/>
       <c r="C101" s="8" t="s">
         <v>26</v>
@@ -2107,7 +2153,7 @@
         <v>11711618</v>
       </c>
     </row>
-    <row r="102" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="16"/>
       <c r="C102" s="8" t="s">
         <v>27</v>
@@ -2119,7 +2165,7 @@
         <v>16454215</v>
       </c>
     </row>
-    <row r="103" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B103" s="16"/>
       <c r="C103" s="8" t="s">
         <v>28</v>
@@ -2131,7 +2177,7 @@
         <v>17544133</v>
       </c>
     </row>
-    <row r="104" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="16"/>
       <c r="C104" s="8" t="s">
         <v>29</v>
@@ -2143,7 +2189,7 @@
         <v>9749468</v>
       </c>
     </row>
-    <row r="105" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B105" s="16"/>
       <c r="C105" s="8" t="s">
         <v>30</v>
@@ -2155,7 +2201,7 @@
         <v>5459503</v>
       </c>
     </row>
-    <row r="106" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B106" s="16"/>
       <c r="C106" s="8" t="s">
         <v>31</v>
@@ -2167,7 +2213,7 @@
         <v>7287089</v>
       </c>
     </row>
-    <row r="107" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B107" s="16"/>
       <c r="C107" s="8" t="s">
         <v>32</v>
@@ -2179,7 +2225,7 @@
         <v>4222943</v>
       </c>
     </row>
-    <row r="108" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108" s="16"/>
       <c r="C108" s="8" t="s">
         <v>33</v>
@@ -2191,7 +2237,7 @@
         <v>7040820</v>
       </c>
     </row>
-    <row r="109" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B109" s="15" t="s">
         <v>42</v>
       </c>
@@ -2205,7 +2251,7 @@
         <v>11417429</v>
       </c>
     </row>
-    <row r="110" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B110" s="16"/>
       <c r="C110" s="8" t="s">
         <v>24</v>
@@ -2217,7 +2263,7 @@
         <v>2506173</v>
       </c>
     </row>
-    <row r="111" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111" s="16"/>
       <c r="C111" s="8" t="s">
         <v>25</v>
@@ -2229,7 +2275,7 @@
         <v>4062368</v>
       </c>
     </row>
-    <row r="112" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B112" s="16"/>
       <c r="C112" s="8" t="s">
         <v>26</v>
@@ -2241,7 +2287,7 @@
         <v>6600796</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113" s="16"/>
       <c r="C113" s="8" t="s">
         <v>27</v>
@@ -2253,7 +2299,7 @@
         <v>9158400</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B114" s="16"/>
       <c r="C114" s="8" t="s">
         <v>28</v>
@@ -2265,7 +2311,7 @@
         <v>6569989</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B115" s="16"/>
       <c r="C115" s="8" t="s">
         <v>29</v>
@@ -2277,7 +2323,7 @@
         <v>3821664</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B116" s="16"/>
       <c r="C116" s="8" t="s">
         <v>30</v>
@@ -2289,7 +2335,7 @@
         <v>2090469</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B117" s="16"/>
       <c r="C117" s="8" t="s">
         <v>31</v>
@@ -2301,7 +2347,7 @@
         <v>3342020</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B118" s="16"/>
       <c r="C118" s="8" t="s">
         <v>32</v>
@@ -2313,7 +2359,7 @@
         <v>2016098</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B119" s="16"/>
       <c r="C119" s="8" t="s">
         <v>33</v>
@@ -2325,8 +2371,8 @@
         <v>2980090</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2"/>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>43</v>
       </c>
@@ -2334,8 +2380,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>45</v>
       </c>
@@ -2343,7 +2389,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>47</v>
       </c>
@@ -2351,7 +2397,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>20</v>
       </c>
@@ -2359,7 +2405,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>36</v>
       </c>
@@ -2367,7 +2413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>37</v>
       </c>
@@ -2375,7 +2421,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>38</v>
       </c>
@@ -2383,7 +2429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>40</v>
       </c>
@@ -2391,7 +2437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>42</v>
       </c>
@@ -2399,7 +2445,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>55</v>
       </c>
@@ -2407,10 +2453,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="13"/>
     </row>
-    <row r="135" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="14" t="s">
         <v>11</v>
       </c>
@@ -2439,75 +2485,1978 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDFE1DC-9F49-4CD0-B3F9-1585FCD533DF}">
+  <dimension ref="A1:E111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="9">
+        <v>172873</v>
+      </c>
+      <c r="E2" s="9">
+        <v>23473512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="9">
+        <v>102392</v>
+      </c>
+      <c r="E3" s="9">
+        <v>11723038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="9">
+        <v>147644</v>
+      </c>
+      <c r="E4" s="9">
+        <v>18161803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="9">
+        <v>165174</v>
+      </c>
+      <c r="E5" s="9">
+        <v>21762413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="9">
+        <v>202226</v>
+      </c>
+      <c r="E6" s="9">
+        <v>28584060</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="9">
+        <v>207257</v>
+      </c>
+      <c r="E7" s="9">
+        <v>30472547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="9">
+        <v>184907</v>
+      </c>
+      <c r="E8" s="9">
+        <v>29020507</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="9">
+        <v>99675</v>
+      </c>
+      <c r="E9" s="9">
+        <v>17678057</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="9">
+        <v>91840</v>
+      </c>
+      <c r="E10" s="9">
+        <v>18753671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="9">
+        <v>74102</v>
+      </c>
+      <c r="E11" s="9">
+        <v>16439405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="9">
+        <v>109480</v>
+      </c>
+      <c r="E12" s="9">
+        <v>22950883</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9">
+        <v>42079</v>
+      </c>
+      <c r="E13" s="9">
+        <v>10767691</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="9">
+        <v>18246</v>
+      </c>
+      <c r="E14" s="9">
+        <v>3849703</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="9">
+        <v>36728</v>
+      </c>
+      <c r="E15" s="9">
+        <v>7736326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="9">
+        <v>51126</v>
+      </c>
+      <c r="E16" s="9">
+        <v>11347135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="9">
+        <v>56766</v>
+      </c>
+      <c r="E17" s="9">
+        <v>14142151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="9">
+        <v>42240</v>
+      </c>
+      <c r="E18" s="9">
+        <v>11442878</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="9">
+        <v>19728</v>
+      </c>
+      <c r="E19" s="9">
+        <v>5445645</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="9">
+        <v>9107</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2588319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="9">
+        <v>8784</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2743955</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="9">
+        <v>4132</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1333113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="9">
+        <v>6496</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2038252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="9">
+        <v>52200</v>
+      </c>
+      <c r="E24" s="9">
+        <v>39061683</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="9">
+        <v>23631</v>
+      </c>
+      <c r="E25" s="9">
+        <v>12527868</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="9">
+        <v>28800</v>
+      </c>
+      <c r="E26" s="9">
+        <v>17158733</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="9">
+        <v>33485</v>
+      </c>
+      <c r="E27" s="9">
+        <v>24662498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="9">
+        <v>29728</v>
+      </c>
+      <c r="E28" s="9">
+        <v>26287600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="9">
+        <v>25954</v>
+      </c>
+      <c r="E29" s="9">
+        <v>19572979</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="9">
+        <v>27819</v>
+      </c>
+      <c r="E30" s="9">
+        <v>19795355</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="9">
+        <v>13311</v>
+      </c>
+      <c r="E31" s="9">
+        <v>10075909</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="9">
+        <v>13715</v>
+      </c>
+      <c r="E32" s="9">
+        <v>13405270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="9">
+        <v>12119</v>
+      </c>
+      <c r="E33" s="9">
+        <v>15425698</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="9">
+        <v>20731</v>
+      </c>
+      <c r="E34" s="9">
+        <v>30950654</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="9">
+        <v>1145</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2607298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="9">
+        <v>321</v>
+      </c>
+      <c r="E36" s="9">
+        <v>398091</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="9">
+        <v>499</v>
+      </c>
+      <c r="E37" s="9">
+        <v>690729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="9">
+        <v>681</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1321961</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="9">
+        <v>720</v>
+      </c>
+      <c r="E39" s="9">
+        <v>2126974</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="9">
+        <v>560</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1707731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="9">
+        <v>439</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1267725</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="9">
+        <v>319</v>
+      </c>
+      <c r="E42" s="9">
+        <v>860823</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="9">
+        <v>467</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1308710</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="9">
+        <v>318</v>
+      </c>
+      <c r="E44" s="9">
+        <v>1117495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="9">
+        <v>402</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1045035</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="9">
+        <v>9420</v>
+      </c>
+      <c r="E46" s="9">
+        <v>8930436</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2465</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1909084</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="9">
+        <v>3930</v>
+      </c>
+      <c r="E48" s="9">
+        <v>2977270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="9">
+        <v>5476</v>
+      </c>
+      <c r="E49" s="9">
+        <v>4736247</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="9">
+        <v>7094</v>
+      </c>
+      <c r="E50" s="9">
+        <v>7340020</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="9">
+        <v>5684</v>
+      </c>
+      <c r="E51" s="9">
+        <v>5895871</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="9">
+        <v>3152</v>
+      </c>
+      <c r="E52" s="9">
+        <v>2213135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="9">
+        <v>1730</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1562845</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2041</v>
+      </c>
+      <c r="E54" s="9">
+        <v>2472381</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="9">
+        <v>1377</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1324973</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="9">
+        <v>2189</v>
+      </c>
+      <c r="E56" s="9">
+        <v>2111180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="9">
+        <v>8607</v>
+      </c>
+      <c r="E57" s="9">
+        <v>12265087</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="9">
+        <v>2901</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2759625</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="9">
+        <v>4241</v>
+      </c>
+      <c r="E59" s="9">
+        <v>4531756</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" s="9">
+        <v>4780</v>
+      </c>
+      <c r="E60" s="9">
+        <v>5438261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="9">
+        <v>5550</v>
+      </c>
+      <c r="E61" s="9">
+        <v>7922004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="9">
+        <v>5792</v>
+      </c>
+      <c r="E62" s="9">
+        <v>8059904</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="9">
+        <v>5108</v>
+      </c>
+      <c r="E63" s="9">
+        <v>5092184</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="9">
+        <v>2733</v>
+      </c>
+      <c r="E64" s="9">
+        <v>3369820</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="9">
+        <v>2856</v>
+      </c>
+      <c r="E65" s="9">
+        <v>4224545</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="9">
+        <v>1670</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2730904</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="9">
+        <v>2624</v>
+      </c>
+      <c r="E67" s="9">
+        <v>4442414</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="9">
+        <v>7041</v>
+      </c>
+      <c r="E68" s="9">
+        <v>6081724</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="9">
+        <v>2172</v>
+      </c>
+      <c r="E69" s="9">
+        <v>1537935</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" s="9">
+        <v>3812</v>
+      </c>
+      <c r="E70" s="9">
+        <v>2556072</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="9">
+        <v>4758</v>
+      </c>
+      <c r="E71" s="9">
+        <v>4864556</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" s="9">
+        <v>5328</v>
+      </c>
+      <c r="E72" s="9">
+        <v>7261274</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="9">
+        <v>5709</v>
+      </c>
+      <c r="E73" s="9">
+        <v>8486286</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="9">
+        <v>5128</v>
+      </c>
+      <c r="E74" s="9">
+        <v>6385102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="9">
+        <v>2900</v>
+      </c>
+      <c r="E75" s="9">
+        <v>3463391</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="9">
+        <v>2792</v>
+      </c>
+      <c r="E76" s="9">
+        <v>4560708</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="9">
+        <v>1670</v>
+      </c>
+      <c r="E77" s="9">
+        <v>2815379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="9">
+        <v>2387</v>
+      </c>
+      <c r="E78" s="9">
+        <v>3465770</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="9">
+        <v>1270</v>
+      </c>
+      <c r="E79" s="9">
+        <v>1135984</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="9">
+        <v>483</v>
+      </c>
+      <c r="E80" s="9">
+        <v>443471</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="9">
+        <v>870</v>
+      </c>
+      <c r="E81" s="9">
+        <v>854886</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="9">
+        <v>1097</v>
+      </c>
+      <c r="E82" s="9">
+        <v>964407</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="9">
+        <v>1293</v>
+      </c>
+      <c r="E83" s="9">
+        <v>1414485</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="9">
+        <v>1242</v>
+      </c>
+      <c r="E84" s="9">
+        <v>1529938</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" s="9">
+        <v>1050</v>
+      </c>
+      <c r="E85" s="9">
+        <v>1256145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="9">
+        <v>486</v>
+      </c>
+      <c r="E86" s="9">
+        <v>647747</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" s="9">
+        <v>538</v>
+      </c>
+      <c r="E87" s="9">
+        <v>922340</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" s="9">
+        <v>344</v>
+      </c>
+      <c r="E88" s="9">
+        <v>731982</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="9">
+        <v>525</v>
+      </c>
+      <c r="E89" s="9">
+        <v>888281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" s="9">
+        <v>11722</v>
+      </c>
+      <c r="E90" s="9">
+        <v>9987208</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="9">
+        <v>5425</v>
+      </c>
+      <c r="E91" s="9">
+        <v>5410888</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" s="9">
+        <v>8795</v>
+      </c>
+      <c r="E92" s="9">
+        <v>8242364</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" s="9">
+        <v>10602</v>
+      </c>
+      <c r="E93" s="9">
+        <v>11711618</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="9">
+        <v>12410</v>
+      </c>
+      <c r="E94" s="9">
+        <v>16454215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" s="9">
+        <v>12149</v>
+      </c>
+      <c r="E95" s="9">
+        <v>17544133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" s="9">
+        <v>9377</v>
+      </c>
+      <c r="E96" s="9">
+        <v>9749468</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97" s="9">
+        <v>4941</v>
+      </c>
+      <c r="E97" s="9">
+        <v>5459503</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E98" s="9">
+        <v>7287089</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D99" s="9">
+        <v>4279</v>
+      </c>
+      <c r="E99" s="9">
+        <v>4222943</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="9">
+        <v>7276</v>
+      </c>
+      <c r="E100" s="9">
+        <v>7040820</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A101" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="9">
+        <v>9283</v>
+      </c>
+      <c r="E101" s="9">
+        <v>11417429</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A102" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" s="9">
+        <v>1906</v>
+      </c>
+      <c r="E102" s="9">
+        <v>2506173</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" s="9">
+        <v>3076</v>
+      </c>
+      <c r="E103" s="9">
+        <v>4062368</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A104" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D104" s="9">
+        <v>3798</v>
+      </c>
+      <c r="E104" s="9">
+        <v>6600796</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A105" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="9">
+        <v>4573</v>
+      </c>
+      <c r="E105" s="9">
+        <v>9158400</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A106" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D106" s="9">
+        <v>4133</v>
+      </c>
+      <c r="E106" s="9">
+        <v>6569989</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A107" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" s="9">
+        <v>3793</v>
+      </c>
+      <c r="E107" s="9">
+        <v>3821664</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A108" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D108" s="9">
+        <v>1995</v>
+      </c>
+      <c r="E108" s="9">
+        <v>2090469</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A109" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109" s="9">
+        <v>2387</v>
+      </c>
+      <c r="E109" s="9">
+        <v>3342020</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A110" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D110" s="9">
+        <v>1657</v>
+      </c>
+      <c r="E110" s="9">
+        <v>2016098</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A111" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" s="9">
+        <v>2462</v>
+      </c>
+      <c r="E111" s="9">
+        <v>2980090</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="4" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
@@ -2515,7 +4464,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
@@ -2523,15 +4472,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G14" s="2"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F17" s="1"/>
     </row>
   </sheetData>
